--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104542_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104542_W10.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9248</v>
+        <v>0.4526</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2446</v>
+        <v>1.6765</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3198</v>
+        <v>-1.224</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.0777</v>
+        <v>0.1449</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1368</v>
+        <v>-1.6515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9408</v>
+        <v>1.7964</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7916</v>
+        <v>1.8208</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0452</v>
+        <v>-0.8898</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7463</v>
+        <v>2.7106</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.8692</v>
+        <v>-1.6759</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1821</v>
+        <v>-0.7617</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6871</v>
+        <v>-0.9143</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7141</v>
+        <v>-0.8305</v>
       </c>
       <c r="T2" t="n">
-        <v>1.107</v>
+        <v>-0.1443</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3929</v>
+        <v>-0.6862</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1542</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.0065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5326</v>
+        <v>0.4348</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9321</v>
+        <v>1.7748</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3995</v>
+        <v>-1.34</v>
       </c>
       <c r="G3" t="n">
-        <v>0.147</v>
+        <v>1.0813</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6522</v>
+        <v>-2.1569</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7992</v>
+        <v>3.2383</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8414</v>
+        <v>3.3614</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.88</v>
+        <v>-0.7347</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7214</v>
+        <v>4.0961</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6944</v>
+        <v>-2.28</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7721</v>
+        <v>-1.4223</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9222</v>
+        <v>-0.8578</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.1184</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0907</v>
+        <v>0.0068</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8393</v>
+        <v>-0.1253</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1548</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0164</v>
+        <v>0.024</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3755</v>
+        <v>0.3306</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.359</v>
+        <v>-0.3066</v>
       </c>
       <c r="G4" t="n">
-        <v>1.084</v>
+        <v>-1.0773</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1572</v>
+        <v>-0.1514</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2413</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3806</v>
+        <v>1.7575</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7242</v>
+        <v>1.0128</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1048</v>
+        <v>0.7447</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2966</v>
+        <v>-2.8348</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.433</v>
+        <v>-1.1642</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8636</v>
+        <v>-1.6706</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-1.8211</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>2.9592</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5414</v>
+        <v>-0.1917</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4174</v>
+        <v>0.2364</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.124</v>
+        <v>-0.4281</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1542</v>
+        <v>0.1548</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1542</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.305</v>
+        <v>-0.0798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3625</v>
+        <v>0.4213</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6675</v>
+        <v>-0.5012</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0023</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5429</v>
+        <v>1.5206</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5406</v>
+        <v>-1.5293</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4325</v>
+        <v>1.3918</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0323</v>
+        <v>1.9953</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4302</v>
+        <v>-1.4006</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9408</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0144</v>
+        <v>-0.7736</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5353</v>
+        <v>-0.4163</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4791</v>
+        <v>-0.3573</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3332</v>
+        <v>-0.3</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2565</v>
+        <v>-0.2615</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0384</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7382</v>
+        <v>-0.7378</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3117</v>
+        <v>-0.3103</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4265</v>
+        <v>-0.4276</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1173</v>
+        <v>-0.1221</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6209</v>
+        <v>-0.6157</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2755</v>
+        <v>-0.2451</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4879</v>
+        <v>-1.9935</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3984</v>
+        <v>-2.7636</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9106</v>
+        <v>0.7701</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.064</v>
+        <v>-2.0597</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4083</v>
+        <v>-1.4074</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.6523</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3369</v>
+        <v>-1.3442</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7272</v>
+        <v>-0.7155</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5762</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2994</v>
+        <v>-0.0536</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2767</v>
+        <v>0.1198</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5826</v>
+        <v>-2.5635</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0549</v>
+        <v>-1.7079</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.8557</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2059</v>
+        <v>-3.1988</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6306</v>
+        <v>-1.6259</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5753</v>
+        <v>-1.5729</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4288</v>
+        <v>-1.4359</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7771</v>
+        <v>-1.7629</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.284</v>
+        <v>-0.2753</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3421</v>
+        <v>-0.0033</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6615</v>
+        <v>-2.6111</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7651</v>
+        <v>-1.3793</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4266</v>
+        <v>-1.2318</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8118</v>
+        <v>-0.7212</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1241</v>
+        <v>1.0366</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6877</v>
+        <v>-1.7578</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9889</v>
+        <v>0.3795</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6958</v>
+        <v>1.4824</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2931</v>
+        <v>-1.1029</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8007</v>
+        <v>-1.1007</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8198</v>
+        <v>-0.4458</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9808</v>
+        <v>-0.6549</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0472</v>
+        <v>-1.1858</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2299</v>
+        <v>-0.5508</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1827</v>
+        <v>-0.635</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.5774</v>
+        <v>-0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.5774</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2475</v>
+        <v>-3.0093</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7056</v>
+        <v>0.5709</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5418</v>
+        <v>-3.5801</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.725</v>
+        <v>-0.8145</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0316</v>
+        <v>-0.1263</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7566</v>
+        <v>-0.6882</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3989</v>
+        <v>0.9613</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4892</v>
+        <v>0.6787</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0903</v>
+        <v>0.2826</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1239</v>
+        <v>-1.7758</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4576</v>
+        <v>-0.805</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6663</v>
+        <v>-0.9708</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8174</v>
+        <v>-0.3088</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9043</v>
+        <v>0.0648</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9131</v>
+        <v>-0.3736</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-2.5689</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-2.5689</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7257</v>
+        <v>-4.0786</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0842</v>
+        <v>-4.2948</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6415</v>
+        <v>0.2162</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7645</v>
+        <v>-1.4263</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0951</v>
+        <v>-1.0976</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3306</v>
+        <v>-0.3288</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4532</v>
+        <v>-0.0229</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5279</v>
+        <v>-0.1346</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0746</v>
+        <v>0.1117</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3113</v>
+        <v>-1.4034</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5672</v>
+        <v>-0.9629</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2559</v>
+        <v>-0.4405</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.0974</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2241</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.369</v>
+        <v>-0.1745</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1449</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>0.1548</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6519</v>
+        <v>-4.227</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9341</v>
+        <v>-1.5694</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2822</v>
+        <v>-2.6576</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4439</v>
+        <v>-1.7682</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1054</v>
+        <v>-2.102</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3384</v>
+        <v>0.3338</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0164</v>
+        <v>-1.4671</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1283</v>
+        <v>-1.5416</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.0745</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4275</v>
+        <v>-0.3011</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9771</v>
+        <v>-0.5604</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4504</v>
+        <v>0.2593</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.083</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6403</v>
+        <v>-0.2799</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8347</v>
+        <v>-0.1024</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1945</v>
+        <v>-0.1775</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1542</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1542</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.091</v>
+        <v>-4.3145</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1948</v>
+        <v>-2.697</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8962</v>
+        <v>-1.6175</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8298</v>
+        <v>0.8361</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4141</v>
+        <v>-2.4099</v>
       </c>
       <c r="I13" t="n">
-        <v>3.244</v>
+        <v>3.246</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4645</v>
+        <v>3.4448</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.603</v>
+        <v>-0.614</v>
       </c>
       <c r="L13" t="n">
-        <v>4.0675</v>
+        <v>4.0588</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6347</v>
+        <v>-2.6087</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.1245</v>
+        <v>-6.146</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4723</v>
+        <v>-0.6829</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6956</v>
+        <v>-0.1535</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.5294</v>
       </c>
       <c r="V13" t="n">
-        <v>0.315</v>
+        <v>0.3126</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1542</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.6125</v>
+        <v>-22.2659</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.948699999999999</v>
+        <v>-9.8994</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.6636</v>
+        <v>-12.3666</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.767899999999999</v>
+        <v>-9.750299999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.461</v>
+        <v>-10.482</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6935000000000002</v>
+        <v>0.7316999999999996</v>
       </c>
       <c r="J14" t="n">
-        <v>8.945800000000002</v>
+        <v>8.724899999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01680000000000026</v>
+        <v>-0.1352000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>8.928799999999999</v>
+        <v>8.860099999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.7137</v>
+        <v>-18.4751</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.4779</v>
+        <v>-10.3467</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.235600000000002</v>
+        <v>-8.1288</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.402499999999999</v>
+        <v>-3.414500000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.2809</v>
+        <v>-19.3487</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.2322</v>
+        <v>-4.9012</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.0565</v>
+        <v>-1.6988</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.1758</v>
+        <v>-3.2025</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.209999999999999</v>
+        <v>-4.200000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2.442499999999999</v>
+        <v>2.4231</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.652699999999999</v>
+        <v>-6.623100000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.426299999999999</v>
+        <v>8.1435</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8549</v>
+        <v>4.7949</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5714</v>
+        <v>3.3486</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9006</v>
+        <v>4.8675</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9411</v>
+        <v>3.916</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9595</v>
+        <v>0.9515</v>
       </c>
       <c r="J15" t="n">
-        <v>5.0305</v>
+        <v>4.9802</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5806</v>
+        <v>3.5433</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1299</v>
+        <v>-0.1127</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>1.07</v>
+        <v>0.8223</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0907</v>
+        <v>0.0926</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.7297</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9673</v>
+        <v>5.5832</v>
       </c>
       <c r="E16" t="n">
-        <v>7.0264</v>
+        <v>4.8701</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9409</v>
+        <v>0.7131</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9653</v>
+        <v>1.9596</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6161</v>
+        <v>1.6142</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3492</v>
+        <v>0.3454</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3001</v>
+        <v>2.2736</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9324</v>
+        <v>1.9165</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3678</v>
+        <v>0.357</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3348</v>
+        <v>-0.3139</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1096</v>
+        <v>1.7421</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5144</v>
+        <v>1.398</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5952</v>
+        <v>0.3441</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4902</v>
+        <v>4.714</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3687</v>
+        <v>2.9362</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1215</v>
+        <v>1.7778</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8746</v>
+        <v>2.8784</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3419</v>
+        <v>1.344</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5327</v>
+        <v>1.5344</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0363</v>
+        <v>3.02</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1617</v>
+        <v>-0.1416</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3907</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6261</v>
+        <v>-0.0351</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0168</v>
+        <v>0.6415</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9395</v>
+        <v>3.5587</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5954</v>
+        <v>1.1537</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3441</v>
+        <v>2.4049</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6039</v>
+        <v>1.6132</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2899</v>
+        <v>0.301</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3141</v>
+        <v>1.3123</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2829</v>
+        <v>1.2678</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3211</v>
+        <v>0.3454</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.33</v>
+        <v>0.2916</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7652</v>
+        <v>-0.1745</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4352</v>
+        <v>0.4661</v>
       </c>
       <c r="V18" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9076</v>
+        <v>1.6085</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4733</v>
+        <v>0.213</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4343</v>
+        <v>1.3955</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1563</v>
+        <v>1.1472</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7245</v>
+        <v>0.7184</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4318</v>
+        <v>0.4289</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2384</v>
+        <v>1.2166</v>
       </c>
       <c r="K19" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0822</v>
+        <v>-0.0694</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7779</v>
+        <v>0.4809</v>
       </c>
       <c r="T19" t="n">
-        <v>0.369</v>
+        <v>0.1345</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4089</v>
+        <v>0.3463</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0758</v>
+        <v>1.2571</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4663</v>
+        <v>0.3429</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6095</v>
+        <v>0.9142</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3702</v>
+        <v>-0.3583</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6573</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1619</v>
+        <v>1.1584</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4156</v>
+        <v>0.4137</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5321</v>
+        <v>-1.5168</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5387</v>
+        <v>0.705</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4386</v>
+        <v>0.3227</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1001</v>
+        <v>0.3823</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8998</v>
+        <v>1.2539</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2359</v>
+        <v>2.0747</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3361</v>
+        <v>-0.8208</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7201</v>
+        <v>2.9169</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1729</v>
+        <v>0.1086</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.893</v>
+        <v>2.8083</v>
       </c>
       <c r="J21" t="n">
-        <v>1.006</v>
+        <v>3.8914</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1905</v>
+        <v>0.9136</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8156</v>
+        <v>2.9778</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7261</v>
+        <v>-0.9745</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0176</v>
+        <v>-0.805</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7086</v>
+        <v>-0.1695</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0321</v>
+        <v>0.0882</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2299</v>
+        <v>0.4596</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1978</v>
+        <v>-0.3714</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.9216</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1717</v>
+        <v>1.1071</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0953</v>
+        <v>-0.1855</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9312</v>
+        <v>-0.7113</v>
       </c>
       <c r="H22" t="n">
-        <v>0.098</v>
+        <v>0.1887</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8333</v>
+        <v>-0.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9269</v>
+        <v>0.9935</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.1896</v>
       </c>
       <c r="L22" t="n">
-        <v>3.0091</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9957</v>
+        <v>-1.7048</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8198</v>
+        <v>-0.0009</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1759</v>
+        <v>-1.7039</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1063</v>
+        <v>0.0395</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4869</v>
+        <v>0.1136</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6194</v>
+        <v>-0.0741</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.272</v>
+        <v>-0.9584</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6944</v>
+        <v>-1.8282</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4224</v>
+        <v>0.8698</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2281</v>
+        <v>0.3192</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1947</v>
+        <v>1.5481</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0334</v>
+        <v>-1.2288</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5069</v>
+        <v>1.6633</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0835</v>
+        <v>1.0752</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4234</v>
+        <v>0.5881</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7212</v>
+        <v>-1.3441</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1113</v>
+        <v>0.4729</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6099</v>
+        <v>-1.8169</v>
       </c>
       <c r="P23" t="n">
-        <v>1.361</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4952</v>
+        <v>3.4145</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7558</v>
+        <v>-0.1881</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9467</v>
+        <v>-0.077</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1909</v>
+        <v>-0.1111</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8589</v>
+        <v>-1.6431</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2162</v>
+        <v>-0.9922</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6427</v>
+        <v>-0.651</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6626</v>
+        <v>-1.6513</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2725</v>
+        <v>0.2837</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9352</v>
+        <v>-1.935</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.451</v>
+        <v>-0.4623</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2116</v>
+        <v>-1.189</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2574</v>
+        <v>0.4634</v>
       </c>
       <c r="T24" t="n">
-        <v>0.369</v>
+        <v>0.6083</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1116</v>
+        <v>-0.1449</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0394</v>
+        <v>-1.8243</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6184</v>
+        <v>-2.3057</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5789</v>
+        <v>0.4814</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3168</v>
+        <v>-3.2308</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5483</v>
+        <v>-0.198</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2315</v>
+        <v>-3.0328</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6884</v>
+        <v>-1.5273</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0941</v>
+        <v>-0.0969</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5944</v>
+        <v>-1.4303</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3716</v>
+        <v>-1.7036</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4542</v>
+        <v>-0.1011</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.8258</v>
+        <v>-1.6025</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>3.4025</v>
+        <v>2.5039</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2636</v>
+        <v>0.1985</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9043</v>
+        <v>0.3597</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3593</v>
+        <v>-0.1612</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>22.6125</v>
+        <v>22.6147</v>
       </c>
       <c r="E26" t="n">
-        <v>12.6636</v>
+        <v>12.3665</v>
       </c>
       <c r="F26" t="n">
-        <v>9.948899999999998</v>
+        <v>10.248</v>
       </c>
       <c r="G26" t="n">
-        <v>9.767700000000001</v>
+        <v>9.750300000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>10.4612</v>
+        <v>10.482</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6933999999999996</v>
+        <v>-0.7314999999999992</v>
       </c>
       <c r="J26" t="n">
-        <v>18.7135</v>
+        <v>18.4752</v>
       </c>
       <c r="K26" t="n">
-        <v>10.4781</v>
+        <v>10.3467</v>
       </c>
       <c r="L26" t="n">
-        <v>8.2357</v>
+        <v>8.128399999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.9458</v>
+        <v>-8.725</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.01689999999999992</v>
+        <v>0.1353999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.928900000000001</v>
+        <v>-8.860099999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>3.402400000000001</v>
+        <v>3.4144</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8785</v>
+        <v>-15.9345</v>
       </c>
       <c r="R26" t="n">
-        <v>19.2808</v>
+        <v>19.3487</v>
       </c>
       <c r="S26" t="n">
-        <v>5.2323</v>
+        <v>5.2498</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1758</v>
+        <v>3.2024</v>
       </c>
       <c r="U26" t="n">
-        <v>2.0565</v>
+        <v>2.0473</v>
       </c>
       <c r="V26" t="n">
-        <v>4.209999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="W26" t="n">
-        <v>6.652699999999999</v>
+        <v>6.6232</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.4426</v>
+        <v>-2.4231</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104542_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104542_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.1548</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.003</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.5689</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.1548</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0.1548</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.623100000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104542_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-2.4231</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
